--- a/results/0916-all/长江下游平原丘陵农畜水产区/tech_selected_summary.xlsx
+++ b/results/0916-all/长江下游平原丘陵农畜水产区/tech_selected_summary.xlsx
@@ -514,211 +514,211 @@
     <t>舟山市区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 0.00</t>
+    <t>0.00</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -760,13 +760,13 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 294359196.47</t>
+    <t>294359196.47</t>
   </si>
   <si>
     <t>incorporation_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 2642277.62</t>
+    <t>2642277.62</t>
   </si>
   <si>
     <t>Acidification_pig</t>
@@ -784,10 +784,10 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 111434605.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 37936307.39</t>
+    <t>111434605.53</t>
+  </si>
+  <si>
+    <t>37936307.39</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -847,7 +847,7 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 168317300.65</t>
+    <t>168317300.65</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -862,7 +862,7 @@
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 108267902.48</t>
+    <t>108267902.48</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -889,7 +889,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 763730870.05</t>
+    <t>763730870.05</t>
   </si>
   <si>
     <t>Biochar_beef cattle</t>
@@ -943,7 +943,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1168017972.89</t>
+    <t>1168017972.89</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -952,7 +952,7 @@
     <t>surface crust cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 90356457.16</t>
+    <t>90356457.16</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -973,7 +973,7 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 251305871.35</t>
+    <t>251305871.35</t>
   </si>
   <si>
     <t>Decreasing grass maturity_sheep &amp; goat</t>
@@ -985,7 +985,7 @@
     <t>sulfate_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 180520783.79</t>
+    <t>180520783.79</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -994,16 +994,16 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 854443371.30</t>
+    <t>854443371.30</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 741844341.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 51505396.27</t>
+    <t>741844341.21</t>
+  </si>
+  <si>
+    <t>51505396.27</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
@@ -1015,7 +1015,7 @@
     <t>cover crop (non-leguminous)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 680582857.62</t>
+    <t>680582857.62</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
@@ -1024,19 +1024,19 @@
     <t>4R(Right time)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 727413787.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 499256109.20</t>
+    <t>727413787.86</t>
+  </si>
+  <si>
+    <t>499256109.20</t>
   </si>
   <si>
     <t>manure（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 58298847.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 100724548.03</t>
+    <t>58298847.16</t>
+  </si>
+  <si>
+    <t>100724548.03</t>
   </si>
   <si>
     <t>Urease Inhibitor_beef cattle</t>
@@ -1045,19 +1045,19 @@
     <t>chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 615180733.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 103430705.31</t>
+    <t>615180733.75</t>
+  </si>
+  <si>
+    <t>103430705.31</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 119098553.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 491102018.31</t>
+    <t>119098553.72</t>
+  </si>
+  <si>
+    <t>491102018.31</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -1069,7 +1069,7 @@
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 614650024.37</t>
+    <t>614650024.37</t>
   </si>
   <si>
     <t>Chemical amendments_poultry</t>
@@ -1078,7 +1078,7 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 183651999.43</t>
+    <t>183651999.43</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -1087,7 +1087,7 @@
     <t>Urease Inhibitor_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 277620355.65</t>
+    <t>277620355.65</t>
   </si>
   <si>
     <t>exhaust air treatment_poultry</t>
@@ -1111,7 +1111,7 @@
     <t>EEF(CRF)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 339059461.70</t>
+    <t>339059461.70</t>
   </si>
   <si>
     <t>compost（add)_vegetable</t>
@@ -1120,7 +1120,7 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 44667598.79</t>
+    <t>44667598.79</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
@@ -1129,34 +1129,34 @@
     <t>biochar_rice</t>
   </si>
   <si>
-    <t>总经济成本: 284217858.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 338020181.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 360090738.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 131957924.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 726652442.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 291201761.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 694042995.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 733671221.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 92781072.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 220669214.04</t>
+    <t>284217858.19</t>
+  </si>
+  <si>
+    <t>338020181.25</t>
+  </si>
+  <si>
+    <t>360090738.97</t>
+  </si>
+  <si>
+    <t>131957924.79</t>
+  </si>
+  <si>
+    <t>726652442.28</t>
+  </si>
+  <si>
+    <t>291201761.25</t>
+  </si>
+  <si>
+    <t>694042995.57</t>
+  </si>
+  <si>
+    <t>733671221.10</t>
+  </si>
+  <si>
+    <t>92781072.25</t>
+  </si>
+  <si>
+    <t>220669214.04</t>
   </si>
   <si>
     <t>cover crop (mix)_vegetable</t>
@@ -1165,43 +1165,43 @@
     <t>cover crop (mix)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 400223621.86</t>
+    <t>400223621.86</t>
   </si>
   <si>
     <t>Algae_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 583318618.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 16925264.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 61049439.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 388910329.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 171986441.85</t>
+    <t>583318618.03</t>
+  </si>
+  <si>
+    <t>16925264.69</t>
+  </si>
+  <si>
+    <t>61049439.28</t>
+  </si>
+  <si>
+    <t>388910329.84</t>
+  </si>
+  <si>
+    <t>171986441.85</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
   </si>
   <si>
-    <t>总经济成本: 190472535.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 172051347.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 188835650.14</t>
-  </si>
-  <si>
-    <t>总经济成本: 193662.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 143671569.30</t>
+    <t>190472535.91</t>
+  </si>
+  <si>
+    <t>172051347.35</t>
+  </si>
+  <si>
+    <t>188835650.14</t>
+  </si>
+  <si>
+    <t>193662.18</t>
+  </si>
+  <si>
+    <t>143671569.30</t>
   </si>
   <si>
     <t>compost（high）≥70%_rice</t>
@@ -1213,22 +1213,22 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 264671180.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 1563546.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 209015539.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 41185682.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 90391981.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 62715863.50</t>
+    <t>264671180.90</t>
+  </si>
+  <si>
+    <t>1563546.07</t>
+  </si>
+  <si>
+    <t>209015539.68</t>
+  </si>
+  <si>
+    <t>41185682.41</t>
+  </si>
+  <si>
+    <t>90391981.77</t>
+  </si>
+  <si>
+    <t>62715863.50</t>
   </si>
   <si>
     <t>Nitrocompounds_beef cattle</t>
@@ -1237,34 +1237,34 @@
     <t>Oil_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 200318699.34</t>
-  </si>
-  <si>
-    <t>总经济成本: 832892044.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 308730999.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 617183283.27</t>
-  </si>
-  <si>
-    <t>总经济成本: 31173885.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 528018392.06</t>
+    <t>200318699.34</t>
+  </si>
+  <si>
+    <t>832892044.93</t>
+  </si>
+  <si>
+    <t>308730999.18</t>
+  </si>
+  <si>
+    <t>617183283.27</t>
+  </si>
+  <si>
+    <t>31173885.88</t>
+  </si>
+  <si>
+    <t>528018392.06</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 227400723.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 139761140.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 96866166.44</t>
+    <t>227400723.72</t>
+  </si>
+  <si>
+    <t>139761140.58</t>
+  </si>
+  <si>
+    <t>96866166.44</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -1285,85 +1285,85 @@
     <t>residue rerention_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 687658553.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 77762067.88</t>
+    <t>687658553.84</t>
+  </si>
+  <si>
+    <t>77762067.88</t>
   </si>
   <si>
     <t>By-products source_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 407364924.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 614172453.97</t>
+    <t>407364924.99</t>
+  </si>
+  <si>
+    <t>614172453.97</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 537981127.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 55461884.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 746030123.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 1490627944.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 81190972.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 109615872.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 258791149.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 86690561.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 315076280.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 376126528.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 225926583.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 158074254.58</t>
+    <t>537981127.89</t>
+  </si>
+  <si>
+    <t>55461884.53</t>
+  </si>
+  <si>
+    <t>746030123.67</t>
+  </si>
+  <si>
+    <t>1490627944.03</t>
+  </si>
+  <si>
+    <t>81190972.72</t>
+  </si>
+  <si>
+    <t>109615872.11</t>
+  </si>
+  <si>
+    <t>258791149.96</t>
+  </si>
+  <si>
+    <t>86690561.85</t>
+  </si>
+  <si>
+    <t>315076280.77</t>
+  </si>
+  <si>
+    <t>376126528.75</t>
+  </si>
+  <si>
+    <t>225926583.35</t>
+  </si>
+  <si>
+    <t>158074254.58</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 244522816.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 141919346.17</t>
+    <t>244522816.97</t>
+  </si>
+  <si>
+    <t>141919346.17</t>
   </si>
   <si>
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 106054556.61</t>
+    <t>106054556.61</t>
   </si>
   <si>
     <t>Acidification_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 432845232.49</t>
+    <t>432845232.49</t>
   </si>
   <si>
     <t>Slatted floor vs Solid floor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 79252956.28</t>
+    <t>79252956.28</t>
   </si>
   <si>
     <t>Feed processing_beef cattle</t>
@@ -1372,67 +1372,67 @@
     <t>Decreasing grass maturity_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 218324659.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 65281245.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 164362135.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 59756291.11</t>
+    <t>218324659.72</t>
+  </si>
+  <si>
+    <t>65281245.25</t>
+  </si>
+  <si>
+    <t>164362135.81</t>
+  </si>
+  <si>
+    <t>59756291.11</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 962230720.16</t>
+    <t>962230720.16</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
   </si>
   <si>
-    <t>总经济成本: 477715186.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 417593304.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 37656002.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 145750060.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 150103.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 38499423.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 33864212.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 2798251.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 55207.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 75556844.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 943633344.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 631108.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 267989.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 9419128.99</t>
+    <t>477715186.54</t>
+  </si>
+  <si>
+    <t>417593304.08</t>
+  </si>
+  <si>
+    <t>37656002.33</t>
+  </si>
+  <si>
+    <t>145750060.86</t>
+  </si>
+  <si>
+    <t>150103.88</t>
+  </si>
+  <si>
+    <t>38499423.64</t>
+  </si>
+  <si>
+    <t>33864212.54</t>
+  </si>
+  <si>
+    <t>2798251.86</t>
+  </si>
+  <si>
+    <t>55207.63</t>
+  </si>
+  <si>
+    <t>75556844.07</t>
+  </si>
+  <si>
+    <t>943633344.94</t>
+  </si>
+  <si>
+    <t>631108.90</t>
+  </si>
+  <si>
+    <t>267989.61</t>
+  </si>
+  <si>
+    <t>9419128.99</t>
   </si>
 </sst>
 </file>
